--- a/游戏机制/时间与亮度/亮度相关.xlsx
+++ b/游戏机制/时间与亮度/亮度相关.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\游戏机制\时间与亮度\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16686C61-3ED5-42AB-BBA4-1678C970846E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75737ECE-7F0F-4419-A9A3-A2AAC1B233D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3210" windowWidth="19200" windowHeight="10050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>甜浆果</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,14 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可催熟，不接随机刻生长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直接破坏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>竹子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,10 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不接随机刻生长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>草方块、菌丝体</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,6 +108,29 @@
   </si>
   <si>
     <t>方块光(blockLight)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新会破坏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不随机刻生长，可种植存活催熟</t>
+  </si>
+  <si>
+    <t>不随机刻生长，可种植存活催熟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不随机刻生长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亮度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际光照(realBrightness)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -229,13 +240,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -518,12 +529,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="21.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="41.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" style="1"/>
     <col min="5" max="5" width="12.4140625" style="1" customWidth="1"/>
     <col min="6" max="7" width="8.6640625" style="1"/>
@@ -532,6 +543,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
+      <c r="A1" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
@@ -556,7 +570,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -564,118 +578,118 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10" t="s">
+      <c r="B5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10" t="s">
+      <c r="B6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10" t="s">
+      <c r="B7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="6" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="D8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -687,58 +701,63 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="F11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="B5:C5"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="F11:H11"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/游戏机制/时间与亮度/亮度相关.xlsx
+++ b/游戏机制/时间与亮度/亮度相关.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\游戏机制\时间与亮度\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75737ECE-7F0F-4419-A9A3-A2AAC1B233D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0CC8ED-5626-489B-919E-C706603B595B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,14 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>原始光照(rawBrightness)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方块光(blockLight)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新会破坏</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -130,7 +122,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>实际光照(realBrightness)</t>
+    <t>原始亮度(rawBrightness)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方块亮度(blockLight)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际亮度(realBrightness)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -240,13 +240,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -544,7 +544,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -578,118 +578,118 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="9" t="s">
+      <c r="B5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9" t="s">
+      <c r="B8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
       <c r="H9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -703,37 +703,37 @@
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10" t="s">
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11" t="s">
+      <c r="F12" s="11"/>
+      <c r="G12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="7" t="s">
@@ -742,11 +742,9 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="B5:C5"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="B6:C6"/>
@@ -755,9 +753,11 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="F11:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
